--- a/www/download/COUNTRY.DEU.zdW13.xlsx
+++ b/www/download/COUNTRY.DEU.zdW13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>Alemanha</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.731925086265228</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.769088761654336</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.885386722112306</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.898408000431061</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.938262378454218</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.08271977276317</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.11656986865627</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.05752964164908</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.884017010217504</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.803923182782427</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.803793923582443</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.796432000106346</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.72966072452248</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.679902074648032</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.716948695538313</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>37.601</t>
+          <t>-0.303766356481106</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>37.498</t>
+          <t>-0.239629593858325</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37.463</t>
+          <t>-0.136155346657057</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>37.911</t>
+          <t>-0.150073975747319</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>38.424</t>
+          <t>-0.15624432456782</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>39.144</t>
+          <t>-0.206264851981382</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>39.316</t>
+          <t>-0.185235444349331</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>39.096</t>
+          <t>-0.191454313173613</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>38.726</t>
+          <t>-0.296928648534534</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>38.88</t>
+          <t>-0.294522497448843</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>38.835</t>
+          <t>-0.272268352642504</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>39.075</t>
+          <t>-0.293410364870604</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>39.724</t>
+          <t>-0.312354051700689</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>-0.304633552802611</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>-0.275417472368968</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>33.852</t>
+          <t>0.102606664869386</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>33.756</t>
+          <t>0.216136839848883</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>33.647</t>
+          <t>0.391812726716821</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>34.046</t>
+          <t>0.365216115699567</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>34.567</t>
+          <t>0.316483493940632</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>35.229</t>
+          <t>0.244010468311939</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>35.333</t>
+          <t>0.273918328712936</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>35.093</t>
+          <t>0.298448745635467</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>34.653</t>
+          <t>0.135939169003017</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>34.658</t>
+          <t>0.103615585132649</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>34.48</t>
+          <t>0.152172573017543</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>34.684</t>
+          <t>0.161126251490077</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>35.288</t>
+          <t>0.148477794560005</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>35.843</t>
+          <t>0.158416121889</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>35.862</t>
+          <t>0.204628269019782</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>57679.197</t>
+          <t>0.611205105295192</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>56921.734</t>
+          <t>0.815081008193014</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>56526.422</t>
+          <t>1.10046241749652</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>56997.003</t>
+          <t>1.03380104706716</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>57318.04</t>
+          <t>0.958074167815673</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>57658.023</t>
+          <t>0.872532209182293</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>57334.344</t>
+          <t>0.901277471350968</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>56510</t>
+          <t>0.905698099497935</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>55724</t>
+          <t>0.63230122335252</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>56044</t>
+          <t>0.726017981930652</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>55693</t>
+          <t>0.726816423703622</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>55862</t>
+          <t>0.737286438393008</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>56788</t>
+          <t>0.67882501697511</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>57721.711</t>
+          <t>0.739898473426623</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>56739.567</t>
+          <t>0.871342037038231</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>49333.493</t>
+          <t>72389762454.2395</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>48495.041</t>
+          <t>66805841287.5726</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>47917.779</t>
+          <t>63726939060.3875</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>48296.046</t>
+          <t>66053618314.3027</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>48623.541</t>
+          <t>66194420150.4384</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>48867.203</t>
+          <t>69960666490.0388</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>48588.388</t>
+          <t>66600504264.6032</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>47915</t>
+          <t>63704420449.0245</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>47126</t>
+          <t>68145661130.6113</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>47259</t>
+          <t>71544644324.4334</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>46689</t>
+          <t>70684882283.4497</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>46883</t>
+          <t>74998583193.486</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>47776</t>
+          <t>78948727034.0849</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>48410</t>
+          <t>79952351047.7453</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>46952.701</t>
+          <t>67029652141.5665</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>48292439560.8063</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>43046638167.1699</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>37196778989.9941</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>30.92</t>
+          <t>38704486031.4942</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>30.07</t>
+          <t>39934625042.344</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>30.27</t>
+          <t>42390497869.207</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>30.73</t>
+          <t>41282205426.3496</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>40559615980.8762</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>33.76</t>
+          <t>46314619660.5257</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>34.11</t>
+          <t>47216657223.1253</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>33.97</t>
+          <t>44736843031.9826</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>45058934252.2315</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>46909022578.1856</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>47269399580.8871</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>36.26</t>
+          <t>44312542215.4257</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>59.45</t>
+          <t>694473.424987196</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>59.53</t>
+          <t>671653.385582668</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>59.47</t>
+          <t>724189.465736388</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>58.47</t>
+          <t>739917.097411536</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>768905.688228584</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>58.38</t>
+          <t>886911.53903242</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>57.85</t>
+          <t>853065.99585364</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>56.95</t>
+          <t>793611.712230884</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>55.05</t>
+          <t>709127.957196003</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>674860.892978538</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>54.99</t>
+          <t>654160.230866315</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>55.31</t>
+          <t>637967.054500793</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>55.78</t>
+          <t>577977.026624917</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>516994.734209257</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>54.49</t>
+          <t>530168.285261084</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>263186.706702958</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>256541.652087</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>251990.413214862</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>249871.577758975</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>257450.663667416</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>259877.850091066</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>248029.778496949</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>248059.894735753</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>11.19</t>
+          <t>261070.664426467</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>287950.786454954</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>304180.712637593</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>317073.389848181</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>361632.215859361</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>395257.163424851</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>356195.52082517</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>623744.113875304</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>19.58</t>
+          <t>579750.662264261</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>551257.247681793</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>565619.760625302</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20.56</t>
+          <t>589592.142784104</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>633442.442632405</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>585639.66675259</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>21.34</t>
+          <t>572401.434571543</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>22.79</t>
+          <t>656414.985927404</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>758011.616126745</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>802118.426921584</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>888484.643945606</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>1053817.87793964</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>22.71</t>
+          <t>1168403.11005509</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>913142.1513752</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>63.61</t>
+          <t>0.0215572843503791</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>63.71</t>
+          <t>0.126569768257979</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>63.71</t>
+          <t>0.288223881061056</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>63.11</t>
+          <t>0.247815197787071</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>62.81</t>
+          <t>0.217578511202642</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>0.152786731533638</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>61.95</t>
+          <t>0.176981404274808</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>0.181347476825025</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>60.88</t>
+          <t>0.0175188816279079</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>60.81</t>
+          <t>0.000896776251537501</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>0.0436364489694054</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>0.0404817774330326</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>61.89</t>
+          <t>0.0184821037438883</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>61.97</t>
+          <t>0.0241297843684503</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>61.08</t>
+          <t>0.0595804033846421</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>16.71</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16.61</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>16.63</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>17.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.731925086265228</t>
+          <t>1426.5756694082</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.769088761654336</t>
+          <t>1275.22923827379</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.885386722112306</t>
+          <t>1105.50060896942</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.898408000431061</t>
+          <t>1136.82917322135</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262378454218</t>
+          <t>1155.28177285689</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271977276317</t>
+          <t>1203.28416557969</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656986865627</t>
+          <t>1168.37532692807</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752964164908</t>
+          <t>1155.77511130072</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017010217504</t>
+          <t>1336.52554354675</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923182782427</t>
+          <t>1362.35954824645</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793923582443</t>
+          <t>1297.47224570715</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796432000106346</t>
+          <t>1299.12738589066</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.72966072452248</t>
+          <t>1329.31938840925</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902074648032</t>
+          <t>1318.79026813847</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948695538313</t>
+          <t>1235.64787363373</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.363</t>
+          <t>54661000024.6289</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>49994332171.6063</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.143</t>
+          <t>43275949174.2458</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>47129572439.6051</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.131</t>
+          <t>48105117643.6267</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.017</t>
+          <t>50157248685.1297</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.005</t>
+          <t>52450174830.702</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.068</t>
+          <t>58082897114.0542</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.282</t>
+          <t>68160037918.1215</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>74660499221.1536</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.407</t>
+          <t>72393107208.2935</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.444</t>
+          <t>75236363042.6597</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>82141023056.1757</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.809</t>
+          <t>79773135076.1017</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.735</t>
+          <t>68917358866.332</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>56817138926.1144</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.502</t>
+          <t>52117577089.7328</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>45218424350.0086</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.326</t>
+          <t>49368794527.5804</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.302</t>
+          <t>51043265689.141</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.173</t>
+          <t>52799433836.7253</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>55401123110.0832</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>59099421681.9492</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>70180340763.0154</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>76531311620.9378</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.638</t>
+          <t>74255668052.3925</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.677</t>
+          <t>76309730724.8216</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.876</t>
+          <t>83030485916.3173</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2.097</t>
+          <t>80303502864.3141</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2.018</t>
+          <t>68829633286.4691</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>8.512</t>
+          <t>-2156138901.48545</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.276</t>
+          <t>-2123244918.12655</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>7.367</t>
+          <t>-1942475175.76281</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>7.401</t>
+          <t>-2239222087.97536</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>7.184</t>
+          <t>-2938148045.5143</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6.412</t>
+          <t>-2642185151.59564</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>6.311</t>
+          <t>-2950948279.38121</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>6.739</t>
+          <t>-1016524567.89497</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>8.105</t>
+          <t>-2020302844.89394</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>9.144</t>
+          <t>-1870812399.78426</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>9.183</t>
+          <t>-1862560844.09894</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>9.438</t>
+          <t>-1073367682.16189</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>10.884</t>
+          <t>-889462860.141599</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-530367788.212387</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>87725579.8628765</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>1457.32876676096</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4.148</t>
+          <t>1436.6347074379</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3.708</t>
+          <t>1424.13228500195</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>3.767</t>
+          <t>1418.55271963332</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3.738</t>
+          <t>1406.64626101464</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.399</t>
+          <t>1387.13002034479</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.374</t>
+          <t>1375.15603300784</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3.535</t>
+          <t>1365.37201151227</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>4.292</t>
+          <t>1359.93997633683</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4.871</t>
+          <t>1363.58127993537</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>5.034</t>
+          <t>1354.08932714617</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>5.362</t>
+          <t>1351.71837158344</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>6.162</t>
+          <t>1353.88800725459</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>6.788</t>
+          <t>1350.61239293586</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>5.914</t>
+          <t>1309.2682723862</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2.284</t>
+          <t>1533.98039249364</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2.208</t>
+          <t>1517.99387592874</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.959</t>
+          <t>1508.85998607759</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.979</t>
+          <t>1503.44235262091</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.929</t>
+          <t>1491.72495723628</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>1472.97217365366</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.706</t>
+          <t>1458.29544063867</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.828</t>
+          <t>1445.41641088602</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2.205</t>
+          <t>1438.92991788463</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2.486</t>
+          <t>1441.46090534979</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2.518</t>
+          <t>1434.0929573838</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2.635</t>
+          <t>1429.60972488804</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2.989</t>
+          <t>1429.56399154164</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>3.272</t>
+          <t>1426.97651540863</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2.986</t>
+          <t>1388.98140909664</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-30.38</t>
+          <t>577907.20701724</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-23.96</t>
+          <t>581114.496989226</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-13.62</t>
+          <t>569372.66299253</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-15.01</t>
+          <t>600858.480607013</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-15.62</t>
+          <t>600302.862251976</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-20.63</t>
+          <t>614536.849060768</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-18.52</t>
+          <t>636044.31902115</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-19.15</t>
+          <t>695201.351947121</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-29.69</t>
+          <t>839065.950346315</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-29.45</t>
+          <t>1007507.32754731</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-27.23</t>
+          <t>1095999.9529517</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-29.34</t>
+          <t>1258715.0600739</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-31.24</t>
+          <t>1510355.82197752</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-30.46</t>
+          <t>1671979.62800848</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-27.54</t>
+          <t>1265888.36750474</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>14695366682.8208</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>21.61</t>
+          <t>14209084809.3418</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>39.18</t>
+          <t>14549014497.4571</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>36.52</t>
+          <t>15881877716.7687</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>16265873190.4625</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>18670370408.8239</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>18679719612.7991</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>29.84</t>
+          <t>18586614054.3795</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>13.59</t>
+          <t>20318891090.0411</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>22838499215.9562</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>15.22</t>
+          <t>23684171362.7852</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>26552838753.4738</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>14.85</t>
+          <t>28931887481.6009</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>29797146401.579</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>23104263486.4485</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>61.12</t>
+          <t>504027.545040582</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>81.51</t>
+          <t>498306.496186612</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>110.05</t>
+          <t>483107.582522955</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>103.38</t>
+          <t>510269.044784054</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>95.81</t>
+          <t>520999.817854744</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>87.25</t>
+          <t>548615.686679205</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>90.13</t>
+          <t>543158.262380266</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>90.57</t>
+          <t>547031.874859046</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>63.23</t>
+          <t>670655.969606237</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>789020.360184291</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>865640.065505454</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>73.73</t>
+          <t>1003709.30337883</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>67.88</t>
+          <t>1170974.86363347</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>73.99</t>
+          <t>1323009.70758408</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>87.13</t>
+          <t>1004959.19095404</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>57679.197</t>
+          <t>59174328879.6641</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>56921.734</t>
+          <t>53257157186.3421</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>56526.422</t>
+          <t>47386211396.6735</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>56997.003</t>
+          <t>51383901351.2356</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>57318.04</t>
+          <t>53952678065.188</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>57658.023</t>
+          <t>60058864544.5441</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>57334.344</t>
+          <t>58111971029.1311</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>56510</t>
+          <t>56134020996.6162</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>55724</t>
+          <t>66303697751.3791</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>56044</t>
+          <t>71040988375.9821</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>55693</t>
+          <t>70241968091.0702</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>55862</t>
+          <t>75631318912.0986</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>56788</t>
+          <t>80261560362.9268</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>57721.711</t>
+          <t>81047847259.1395</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>56739.567</t>
+          <t>68534934974.6845</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>49333.493</t>
+          <t>73879.6619766577</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48495.041</t>
+          <t>82808.0008026142</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>47917.779</t>
+          <t>86265.0804695758</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>48296.046</t>
+          <t>90589.4358229591</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>48623.541</t>
+          <t>79303.0443972323</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>48867.203</t>
+          <t>65921.1623815622</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>48588.388</t>
+          <t>92886.0566408838</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>47915</t>
+          <t>148169.477088074</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>47126</t>
+          <t>168409.980740078</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>47259</t>
+          <t>218486.967363019</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>46689</t>
+          <t>230359.88744625</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>46883</t>
+          <t>255005.756695061</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>47776</t>
+          <t>339380.958344055</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>48410</t>
+          <t>348969.920424398</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>46952.701</t>
+          <t>260929.176550695</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>72389.762</t>
+          <t>-44478962196.8433</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>66805.841</t>
+          <t>-39048072377.0003</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>63726.939</t>
+          <t>-32837196899.2164</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>66053.618</t>
+          <t>-35502023634.4669</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>66194.42</t>
+          <t>-37686804874.7255</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>69960.666</t>
+          <t>-41388494135.7202</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>66600.504</t>
+          <t>-39432251416.332</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>63704.42</t>
+          <t>-37547406942.2367</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>68145.661</t>
+          <t>-45984806661.338</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>71544.644</t>
+          <t>-48202489160.0259</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>70684.882</t>
+          <t>-46557796728.285</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>74998.583</t>
+          <t>-49078480158.6248</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>78948.727</t>
+          <t>-51329672881.326</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>79952.351</t>
+          <t>-51250700857.5605</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>67029.652</t>
+          <t>-45430671488.236</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>1056023.36682</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1007321.96497</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>890469.64307</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>897064.59083</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>862328.08299</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>768933.95974</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.586</t>
+          <t>758537.39575</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.572</t>
+          <t>805528.24857</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.656</t>
+          <t>961033.54614</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.758</t>
+          <t>1094768.77747</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>1105569.44245</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.888</t>
+          <t>1168674.7893</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.054</t>
+          <t>1341856.5192</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1.168</t>
+          <t>1447149.57748</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>1255690.97522</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>30544.614</t>
+          <t>0.0852957412890686</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>29561.813</t>
+          <t>0.0852134690149359</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>29130.824</t>
+          <t>0.0871501306068368</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>29180.243</t>
+          <t>0.0881949988800552</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>28904.383</t>
+          <t>0.0872699859172129</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>28702.257</t>
+          <t>0.0845016252336804</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>28206.608</t>
+          <t>0.0867785854780721</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>27607.394</t>
+          <t>0.0887810568380587</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>27103.027</t>
+          <t>0.0895304775734942</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>27178.128</t>
+          <t>0.092613961196142</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>26805.241</t>
+          <t>0.0958433306275761</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>26764.734</t>
+          <t>0.101490220093738</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>27092.35</t>
+          <t>0.102255958645864</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>27046.949</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>26146.709</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>1363254.26397007</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>1310121.86457592</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>1142969.47780482</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>1150434.99498854</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>1130675.20037073</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>1017493.19579972</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>1005060.25879547</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>1068159.18640789</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>1281841.85530205</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>1415296.91437412</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>1406878.01531334</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>1443676.29595017</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>1617724.45786562</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>1809250.3412473</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>1734712.46695596</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>48292.44</t>
+          <t>1557974.55406545</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>43046.638</t>
+          <t>1502412.29547561</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>37196.779</t>
+          <t>1317411.14858811</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>38704.486</t>
+          <t>1326358.61866775</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>39934.625</t>
+          <t>1302406.93863858</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>42390.498</t>
+          <t>1172559.80554357</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>41282.205</t>
+          <t>1158039.93511591</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>40559.616</t>
+          <t>1229729.51173504</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>46314.62</t>
+          <t>1479553.94155057</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>47216.657</t>
+          <t>1638875.00976356</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>44736.843</t>
+          <t>1637759.62104069</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>45058.934</t>
+          <t>1677285.14398029</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>46909.023</t>
+          <t>1875703.64141804</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>47269.4</t>
+          <t>2097001.03153539</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>44312.542</t>
+          <t>2017691.93984275</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>8511749.96256924</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>12.66</t>
+          <t>8276300.33663781</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>28.82</t>
+          <t>7366901.39568792</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>24.78</t>
+          <t>7401377.1805815</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>21.76</t>
+          <t>7184357.139993</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>15.28</t>
+          <t>6412025.09902104</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>6310558.6501231</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>6738992.81156657</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>8104710.03110398</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>9144246.35647392</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>9183339.8407178</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>9437534.09870476</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>10884321.7521092</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>1557974.55406545</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>1565823.16105272</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.724</t>
+          <t>1574515.97314039</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>1595825.50331131</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>1633583.99896788</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.887</t>
+          <t>1711168.19227524</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.853</t>
+          <t>1722289.03455401</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.794</t>
+          <t>1709599.1639397</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>1698931.65152834</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.675</t>
+          <t>1698284.98947203</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.654</t>
+          <t>1692748.03649668</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>1718338.36227257</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.578</t>
+          <t>1746733.59539946</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>1812032.68718169</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1812740.50663989</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1363254.26397007</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1366629.34788592</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1367887.27938545</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1385840.64218068</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1418319.0540482</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1487220.49170109</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1498136.42213078</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1487260.39086597</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1473349.9808319</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1466778.69985087</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>1452908.41558482</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>1479614.55459368</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>1510272.60285515</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>1567941.67538722</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1559966.69082129</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>726016.022724546</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>705252.26229439</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>642026.418801891</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>652764.452152251</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>626978.746431417</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>541826.541906429</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>547621.353234095</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>598294.903834961</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>725618.559679428</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>846884.877226439</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>880161.876619309</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>957817.412819707</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1112986.75497196</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>1175234.90225461</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>968030.770867249</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>49333493412.3921</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>48495041184.2737</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>47917778993.4606</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>48296045892.6359</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>48623541304.493</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>48867203486.7267</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>48588388114.2661</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>4.7915e+10</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>4.7126e+10</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>4.7259e+10</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>4.6689e+10</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>4.6883e+10</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>4.7776e+10</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>4.841e+10</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>46952701355.6198</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>57679196738.1535</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>56921734359.5757</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>56526421658.4249</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>56997003030.2113</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>57318039756.847</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>57658022765.4988</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>57334343544.1498</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>5.651e+10</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>5.5724e+10</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>5.6044e+10</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>5.5693e+10</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>5.5862e+10</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>5.6788e+10</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>57721710897.5781</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>56739567063.1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>30544613977.9518</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>29561813394.1238</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>29130823720.2806</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>29180242583.1754</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>28904383491.8446</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>28702256708.3024</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>28206607677.6067</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>27607393826.0056</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>27103026912.1813</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>27178127830.1887</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>26805241151.4865</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>26764733829.6882</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>27092350295.3203</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>27046949132.8123</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>26146708723.6509</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>37601000</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>37498000</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>37463000</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>37911000</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>38424000</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>39144000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>39316000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>39096000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>38726000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>38880000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>38835000</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>39075000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>39724000</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>40450357.994188</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>40849767.096668</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>33852000</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>33756000</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>33647000</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>34046000</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>34567000</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>35229000</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>35333000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>35093000</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>34653000</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>34658000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>34480000</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>34684000</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>35288000</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>35843000</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>35861788.1040119</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>57679196738.1535</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>56921734359.5757</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>56526421658.4249</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>56997003030.2113</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>57318039756.847</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>57658022765.4988</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>57334343544.1498</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>5.651e+10</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>5.5724e+10</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>5.6044e+10</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>5.5693e+10</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>5.5862e+10</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>5.6788e+10</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>57721710897.5781</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>56739567063.1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>49333493412.3921</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>48495041184.2737</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>47917778993.4606</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>48296045892.6359</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>48623541304.493</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>48867203486.7267</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>48588388114.2661</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>4.7915e+10</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>4.7126e+10</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>4.7259e+10</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>4.6689e+10</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>4.6883e+10</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>4.7776e+10</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>4.841e+10</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>46952701355.6198</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.292360206508077</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.294446300408508</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.296502004060942</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.309167344856546</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.300709474163641</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.302691879989424</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.307297726488227</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.318450369437362</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.337570238433673</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.341056812054553</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.339734656467144</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.338469540174099</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.337491902506053</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.347081543739561</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.36261815887713</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.59454138680484</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.595258406339624</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.594653617929654</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.584727948123357</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.588371699399295</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.583821059901513</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.578503908321464</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.569470000808505</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.550528974734686</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.560057982965693</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.549858319779674</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.55309471873137</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.557789083181953</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.555608619892097</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.54494562514477</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.113098406687083</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.110295293251868</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.108844378009404</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.106104707020097</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.110918826437064</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.113487060109063</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.114198365190309</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.112079629754133</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.111900786831642</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0988852049797545</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.110407023753181</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.108435741094531</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.104719014311994</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0973098363683425</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0924362159780996</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.195115628492194</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.195838904275002</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.196825263313754</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.208303944300909</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.20555775804634</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.204559713203882</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.208305012463317</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.213422469992099</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.227905040231277</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.233830997800985</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.22946619900437</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.22343403545077</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.220789162547975</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.227133454897749</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.24001300599493</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.63606301929354</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.637096976669119</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.637065756539099</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.631067282541124</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.628112529655099</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.623163264316266</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.619472028944092</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.618968233794798</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.608778533378536</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.608101359468275</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.599776482128622</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.606592253844489</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.618927960349674</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.619677145111692</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.610837209615879</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.168821352214266</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.167064119055879</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.166108980147147</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.160628773157967</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.166329712298562</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.172277022479852</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.172222958592591</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.167609296213104</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.163316426390187</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.15806764273074</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.170757318867008</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.169973710704741</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.160282877102351</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.153189399990559</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.149149784389191</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>4289714.99955</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>4148350.8472</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>3708413.41752</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>3767286.13336</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>3737973.56792</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>3399402.20853</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3373850.6568</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>3534860.73441</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>4292179.88478</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>4871137.04873</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>5034337.63434</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>5362002.02775</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>6161850.08853</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>6788492.30254</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>5913505.46421</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2283990.57679</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2207664.55777</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1959437.56739</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1979123.07082</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1929385.68507</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1714386.34745</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1705661.28835</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1828024.41557</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2205172.50123</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2485759.88699</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2517921.49766</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2635102.5568</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2988690.39639</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>3272235.93379</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2985722.71071</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>6229963.21060905</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>6404784.34412815</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>6577082.45551666</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>6759822.08704437</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>6956322.46315011</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>7155973.14476165</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>7327014.06849413</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>7460931.2845158</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>7586839.43485666</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>7701435.24330397</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>7833162.16535079</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>8009309.99162415</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>8201285.55467841</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW13</t>
